--- a/Versuchsprotokoll.xlsx
+++ b/Versuchsprotokoll.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chemtherm.sharepoint.com/sites/Steuerungen/Freigegebene Dokumente/Python/Steuerung_Verdampfer/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ChemTherm 006\Documents\GITKRAKEN\Steuerung_Verdampfer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="11_0C781E5B5CB47D2367647D28A3DCAB387539FF97" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC948F95-3E8E-4D04-93B9-5616C028FE1B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEC50C7E-6606-4545-A1F9-B977B67420A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1950" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Übersicht" sheetId="2" r:id="rId1"/>
@@ -69,10 +69,10 @@
     <t>[°C]</t>
   </si>
   <si>
-    <t>[ml/min]</t>
-  </si>
-  <si>
     <t>Gesamtzeit</t>
+  </si>
+  <si>
+    <t>[l/min]</t>
   </si>
 </sst>
 </file>
@@ -521,22 +521,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>1</v>
       </c>
@@ -544,7 +544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -560,22 +560,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B1">
         <f>SUM(A:A)/60</f>
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -586,7 +586,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>7</v>
       </c>
@@ -594,22 +594,22 @@
         <v>8</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="8">
-        <v>1800</v>
+        <v>900</v>
       </c>
       <c r="B4" s="9">
         <v>140</v>
       </c>
       <c r="C4" s="8">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D4" s="8"/>
     </row>
-    <row r="5" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
         <v>1800</v>
       </c>
@@ -617,56 +617,56 @@
         <v>160</v>
       </c>
       <c r="C5" s="8">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D5" s="8"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="8"/>
       <c r="D7" s="8"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="8"/>
       <c r="D8" s="8"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="D9" s="8"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="8"/>
       <c r="D10" s="8"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="8"/>
       <c r="D11" s="8"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="8"/>
       <c r="D12" s="8"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="8"/>
       <c r="D13" s="8"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="8"/>
       <c r="D14" s="8"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="D16" s="8"/>
     </row>
   </sheetData>
